--- a/docs/_baseline/habitat_zero_report.xlsx
+++ b/docs/_baseline/habitat_zero_report.xlsx
@@ -1,14 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <bookViews>
-    <workbookView activeTab="3"/>
-  </bookViews>
   <sheets>
     <sheet sheetId="1" name="조사개황" state="visible" r:id="rId1"/>
     <sheet sheetId="2" name="평가항목" state="visible" r:id="rId2"/>
     <sheet sheetId="3" name="건강성평가(HRI)" state="visible" r:id="rId3"/>
-    <sheet sheetId="4" name="License" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">평가항목!$A$3:$K$13</definedName>
@@ -18,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81">
   <si>
     <t>서식·수변환경 조사결과 — 조사개황</t>
   </si>
@@ -261,9 +257,6 @@
   </si>
   <si>
     <t>E</t>
-  </si>
-  <si>
-    <t>Thank you for using version 2026.2.519.80 of Telerik Document Processing Libraries. License validation couldn't run, possibly due to a missing Telerik.Licensing NuGet package reference to BaselineGen. See documentation for setup. Learn more about Telerik Document Processing Libraries licensing https://docs.telerik.com/devtools/document-processing/distribution-and-licensing/license-key</t>
   </si>
 </sst>
 </file>
@@ -271,7 +264,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <b val="false"/>
       <i val="false"/>
@@ -329,15 +322,6 @@
       <color rgb="FFB71C1C"/>
       <name val="맑은 고딕"/>
     </font>
-    <font>
-      <b val="false"/>
-      <i val="false"/>
-      <u val="none"/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -370,7 +354,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true"/>
     <xf numFmtId="0" fontId="1" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="2" borderId="0" xfId="0" applyFont="true"/>
@@ -389,7 +373,6 @@
     <xf numFmtId="0" fontId="6" borderId="0" xfId="0" applyFont="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" borderId="0" xfId="0" applyFont="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1412,19 +1395,4 @@
   <autoFilter ref="A3:T4"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.6999999999999998" right="0.6999999999999998" top="0.75"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <sheetFormatPr customHeight="false" defaultColWidth="9.28125" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="10" t="s">
-        <v>81</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.6999999999999998" right="0.6999999999999998" top="0.75"/>
-</worksheet>
 </file>
--- a/docs/_baseline/habitat_zero_report.xlsx
+++ b/docs/_baseline/habitat_zero_report.xlsx
@@ -91,7 +91,7 @@
     <t>곡교천</t>
   </si>
   <si>
-    <t>평지형</t>
+    <t>지류</t>
   </si>
   <si>
     <t>온양</t>
